--- a/report.xlsx
+++ b/report.xlsx
@@ -413,354 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>test_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>username</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>expected</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>test_login[tc0]</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>valid login</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>tomsmith</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>test_login[tc1]</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>invalid username</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>wronguser</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>test_login[tc2]</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>invalid password</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>tomsmith</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>test_login[tc3]</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>empty username</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>test_login[tc4]</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>empty password</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>tomsmith</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>test_login[tc5]</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>empty username and password</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>test_login[tc6]</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>username with special characters</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>tom@smith</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>test_login[tc7]</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>password with special characters</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>tomsmith</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>test_login[tc8]</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>long username</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>thisisaverylongusernamethatexceedsthemaximumlength</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>test_login[tc9]</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>long password</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>tomsmith</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>failure</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>